--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/operating_costs_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/operating_costs_timeline.xlsx
@@ -85,7 +85,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -127,7 +127,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -139,12 +139,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -169,7 +169,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/working hours 04.2025.xlsx</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -181,12 +181,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -196,7 +196,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>991.96</t>
+          <t/>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -211,19 +211,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/307538032.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/working hours 06.2025  Копие.xlsx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -253,7 +253,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/38389 - Vorgangsmappe Lohn - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/working hours 12.2024.xlsx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -265,12 +265,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -280,7 +280,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>10.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -295,24 +295,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -322,7 +322,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -332,12 +332,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -349,7 +349,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -364,7 +364,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5270.35</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -374,12 +374,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>1.23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/6106074_020725.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -391,12 +391,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -406,7 +406,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9949.77</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -421,7 +421,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/6106074_040625.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -433,12 +433,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -448,7 +448,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1599.35</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/6106074_050825.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -475,12 +475,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18535.34</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/6106074_061224.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18262.14</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>-30.30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/6106074_070225.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -559,12 +559,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17862.56</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/6106074_080125.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -601,12 +601,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1013.05</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -626,24 +626,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1013.05</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/89878877, Antrag auf Ratenzahlung.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t/>
+          <t>8.09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -673,24 +673,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 01-2025.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24159.32</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 01-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -727,12 +727,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t/>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t/>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t/>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>307809.92</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -836,29 +836,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 03-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 05-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -937,12 +937,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>8.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -967,24 +967,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/aktuelle Unbedenklichkeitsbescheinigungen.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t/>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t/>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1051,24 +1051,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1105,12 +1105,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5236.01</t>
+          <t>13649.05</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t/>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1177,24 +1177,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>13649.05</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t/>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>41544.44</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>13447.05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Aok plus.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t/>
+          <t>88.53</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1345,19 +1345,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Aok Sachsen Anhalt copy document from bank_.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1367,44 +1367,44 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>vertreter</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t/>
+          <t>31.08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>5.20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t/>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/BKK Linde already clear . I paid.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/bonuses 05_2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/UB.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1441,12 +1441,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t/>
+          <t>2052.97</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1471,19 +1471,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/bonuses.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>2912.00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/BWA 03-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/2022 Arbeitgeberbestätigung zu den Arbeitstagen.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>214.00</t>
+          <t>3080.00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t/>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/CarlundCarla_RG424005125.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/2023 Arbeitgeberbestätigung zu den Arbeitstagen.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>89.00</t>
+          <t/>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t/>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1597,24 +1597,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/CarlundCarla_RG424005157.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t/>
+          <t>30281.89</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1634,29 +1634,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t/>
+          <t>10.01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 02.04.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/39922 - Accountings 11-2023.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1666,39 +1666,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t/>
+          <t>25150.59</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t/>
+          <t>17.02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 03.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/40578 - Accountings 12-2023.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>18516.48</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1718,29 +1718,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t/>
+          <t>13.04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 13.03.2025(1).docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t/>
+          <t>30.10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1760,29 +1760,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1792,39 +1792,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>20797.47</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t/>
+          <t>11.03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2024.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1834,34 +1834,34 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t>24159.32</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13447.05</t>
+          <t/>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2025.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t/>
+          <t>22523.36</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1886,29 +1886,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>10.04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/DAK.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>22853.99</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t/>
+          <t>11.06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Docutain Dokument.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 04-2024.pdf</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t/>
+          <t>24018.01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1970,39 +1970,39 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t/>
+          <t>11.07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/enrico_deductions_detailed.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-Id</t>
+          <t/>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>23553.36</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t/>
+          <t>10.08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Favorit MP Martin Zahariev _4025268_vom_01.09.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 06-2024.pdf</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2029,22 +2029,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-Id</t>
+          <t/>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>23067.09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t/>
+          <t>7.09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Favorit MP Martin Zahariev _4026904_vom_01.11.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 07-2024.pdf</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2071,22 +2071,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-Id</t>
+          <t/>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>22536.76</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t/>
+          <t>19.11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Favorit MP Martin Zahariev _4029768_vom_01.03.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 09-2024.pdf</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2113,22 +2113,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-Id</t>
+          <t/>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>24226.58</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t/>
+          <t>10.12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Favorit MP Martin Zahariev _4030475_vom_01.04.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 10-2024.pdf</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2155,22 +2155,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-Id</t>
+          <t/>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>27948.98</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t/>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Favorit MP Martin Zahariev _4033045_vom_01.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2197,22 +2197,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-Id</t>
+          <t/>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>23984.73</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t/>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Favorit MP Martin Zahariev _4034294_vom_01.09.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 12-2024.pdf</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2239,12 +2239,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t/>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t/>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Favorit MP Martin Zahariev _9005483_vom_04.07.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>916.00</t>
+          <t>797.30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>repairs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Voransicht2023_89878877.pdf</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2365,12 +2365,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t/>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>26599.51</t>
+          <t/>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2395,19 +2395,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Health insurance fund reimbursements.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/widerruf_doc.pdf</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Healts Vers..eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/working hours 03.2025.xlsx</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2449,12 +2449,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t/>
+          <t>30.12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Ihre Lohnauswertungen.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/01-2023 #9120.pdf</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t/>
+          <t>8.03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2521,29 +2521,29 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/invoices.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>-ID: DE07ZZZ00000843064</t>
+          <t/>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2558,39 +2558,39 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t/>
+          <t>15.03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Aktivierung Ihres SEPA-Mandats.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/03-2023 #9120.pdf</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-Identifikationsnummer</t>
+          <t/>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2617,7 +2617,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-Identifikationsnummer</t>
+          <t/>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t/>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>-Identifikationsnummer</t>
+          <t/>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-Identifikationsnummer</t>
+          <t/>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t/>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2743,12 +2743,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>12.12</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2768,24 +2768,24 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t/>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KKH(1).eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>435.00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2815,29 +2815,29 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KKH.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t/>
+          <t>-Identifikationsnummer: DE63ZZZ00000008438</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KKH1.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2869,22 +2869,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t/>
+          <t>-Id</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t/>
+          <t>10.99</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2899,34 +2899,34 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Mahnbescheid Amtsgericht Euskirchen _ AXA.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4025268_vom_01.09.2024.pdf</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t/>
+          <t>-Id</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t/>
+          <t>10.99</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2941,34 +2941,34 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Mahnung Finanzamt.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4026904_vom_01.11.2024.pdf</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t/>
+          <t>-Id</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>103.00</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4029768_vom_01.03.2025.pdf</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2995,22 +2995,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t/>
+          <t>-Id</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>95.59</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4030475_vom_01.04.2025.pdf</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3037,22 +3037,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2058-08</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t/>
+          <t>-Id</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>637.84</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4033045_vom_01.08.2025.pdf</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3079,22 +3079,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t/>
+          <t>-Id</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t/>
+          <t>11.99</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3109,24 +3109,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/original_msg(1).eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4034294_vom_01.09.2025.pdf</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3151,29 +3151,29 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/original_msg(2).eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _9005483_vom_04.07.2025.pdf</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t/>
+          <t>-ID: DE07ZZZ00000843064</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/original_msg.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Aktivierung Ihres SEPA-Mandats.PDF</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3205,22 +3205,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t/>
+          <t>-Identifikationsnummer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t/>
+          <t>20.07</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3235,34 +3235,34 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Petya Stefanova AOK.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t/>
+          <t>-Identifikationsnummer</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t/>
+          <t>20.08</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3277,34 +3277,34 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/PQ.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t/>
+          <t>-Identifikationsnummer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3331,22 +3331,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t/>
+          <t>-Identifikationsnummer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>31.08</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/RE-53652_2024 20.09.2024 10_56_50.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung RE211073-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung RE211073.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>797.30</t>
+          <t>895.36</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Remaining health insurances for 09_2024 und 10_2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>895.36</t>
+          <t>812.26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3583,12 +3583,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>546.15</t>
+          <t>2520.00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Schwerbehindertenabgabe _Überweisungsdaten.pdf</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>812.26</t>
+          <t>1680.00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/ueberweisung2022_89878877_20240612110113.pdf</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3667,7 +3667,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t/>
+          <t>Nr.: 2000016306</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2520.00</t>
+          <t>826119991.48</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Schwerbehindertenabgabe _Überweisungsdaten.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Zahlungsavis 8345-1440-1.pdf</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3709,37 +3709,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>vertreter</t>
+          <t/>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t/>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Zahlungsavis Zahariev Juni 2025.pdf</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/UB.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/3.0.2_920_v6.2_20240101_gebuehrenordnung_pq_kep.pdf</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1680.00</t>
+          <t>991.96</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ueberweisung2022_89878877_20240612110113.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3835,22 +3835,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1709.48</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3877,22 +3877,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>147244.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3924,17 +3924,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5349.82</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3961,22 +3961,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>532.95</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4003,22 +4003,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4045,7 +4045,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2052.97</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4087,12 +4087,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>repairs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Voransicht2023_89878877.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4129,12 +4129,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t/>
+          <t>31.07</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4154,39 +4154,39 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/working hours 04.2025(1).xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nr.: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>826119991.48</t>
+          <t>30.08</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Zahlungsavis 8345-1440-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4213,12 +4213,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4228,39 +4228,39 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t/>
+          <t>30.10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2290.99</t>
+          <t/>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Zoll payment.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>18516.48</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml::41467 - Accountings 02-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4297,7 +4297,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml::41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4339,12 +4339,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>22523.36</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml::Accountings 02-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml::46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4423,12 +4423,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>5270.35</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 03-2024.eml::41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_020725.pdf</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4465,12 +4465,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>22853.99</t>
+          <t>9949.77</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t/>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml::Accountings 04-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_040625.pdf</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4507,12 +4507,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>1599.35</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml::42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_050825.pdf</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4549,12 +4549,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>24018.01</t>
+          <t>18535.34</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t/>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 05-2024.eml::Accountings 05-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_061224.pdf</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4591,12 +4591,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>23553.36</t>
+          <t>18262.14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t/>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml::Accountings 06-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_070225.pdf</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4633,12 +4633,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>17862.56</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml::43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_080125.pdf</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>23067.09</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t/>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml::Accountings 07-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/BWA 03-2025.pdf</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4717,12 +4717,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>214.00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t/>
+          <t>18.09</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml::43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4774,22 +4774,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>22536.76</t>
+          <t>89.00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t/>
+          <t>19.09</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t/>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml::Accountings 09-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005157.pdf</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>30.10</t>
+          <t/>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4826,29 +4826,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml::44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2036-08</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>24226.58</t>
+          <t>675.92</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t/>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml::Accountings 10-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4885,12 +4885,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2054-07</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>637.84</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml::45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4927,12 +4927,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2058-08</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>27948.98</t>
+          <t>637.84</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t/>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml::Accountings 11-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4969,12 +4969,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>637.84</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml::45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5011,12 +5011,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>23984.73</t>
+          <t>499.80</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t/>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml::Accountings 12-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5053,12 +5053,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>599.76</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml::46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5095,12 +5095,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20797.47</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t/>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::Accountings 01-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5137,12 +5137,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>523.60</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>8282.40</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>30281.89</t>
+          <t>71.40</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t/>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::39922 - Accountings 11-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5263,12 +5263,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>28.12</t>
+          <t>53.55</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5305,12 +5305,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>30.10</t>
+          <t>9496.20</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5347,12 +5347,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>25150.59</t>
+          <t>333.20</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t/>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings122023.zip::40578 - Accountings 12-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t/>
+          <t>47.60</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5419,19 +5419,19 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/awbonuses042024.zip::Working Hours 04.2024.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t/>
+          <t>166.60</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5461,34 +5461,34 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/awbonuses042024.zip::38389 - Vorgangsmappe Lohn - Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t/>
+          <t>1709.48</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5503,34 +5503,34 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/awbonusfoodbonus032024.zip::38389 - Vorgangsmappe Lohn - Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t/>
+          <t>147244.68</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5545,34 +5545,34 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/awbonusfoodbonus032024.zip::38389 - Vorgangsmappe Lohn - Working Hours 03-2024 .xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>104081.50</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdabrechnungmai2025.zip::Leistungsnachweis Zahariev Mai 25 Sachsenpower GmbH &amp; Co. KG.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5599,22 +5599,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>26176.42</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdabrechnungmai2025.zip::gutschrift 66 Mai 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5641,22 +5641,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>5349.82</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdabrechnungseptember.zip::Leistungsnachweis September 2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5683,22 +5683,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>74.04</t>
+          <t>532.95</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdabrechnungseptember.zip::Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5725,22 +5725,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2912.00</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdbentigtezuarbeitfrdiesteuererklrungvonihrenmi.zip::2022 Arbeitgeberbestätigung zu den Arbeitstagen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5767,22 +5767,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>3080.00</t>
+          <t>2137.23</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdbentigtezuarbeitfrdiesteuererklrungvonihrenmi.zip::2023 Arbeitgeberbestätigung zu den Arbeitstagen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5809,22 +5809,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t/>
+          <t>en-Nr: 2000016306</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>511.46</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::gutschrift 05.04. 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1545.27</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Docutain Dokument.pdf</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5935,12 +5935,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>637.84</t>
+          <t>75.47</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5977,7 +5977,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>74.04</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>523.60</t>
+          <t>916.00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6061,7 +6061,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>8282.40</t>
+          <t>82.85</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2789 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6103,12 +6103,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>71.40</t>
+          <t>97.74</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6145,7 +6145,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>3042.12</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2798 Zahariev Hermes Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6187,7 +6187,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>53.55</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 66 Mai 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>97.74</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6271,7 +6271,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>10390.09</t>
+          <t>76.54</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift April 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6313,7 +6313,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>196.35</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift märz 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6355,7 +6355,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6397,22 +6397,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2137.23</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen012024350690382950.zip::Unternehmerabrechnung - VP 120-2400035414.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Dezember Zahariev 2024.pdf</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6439,22 +6439,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>511.46</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen012024350690382950.zip::Unternehmerabrechnung - VP 120-2400035649.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Martin Zahariev Februar 2025.pdf</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6481,22 +6481,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>104081.50</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen0120243506903829501.zip::Unternehmerabrechnung - VP 120-2400000826.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Martin Zahariev Januar 2025.pdf</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6523,22 +6523,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>26176.42</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen0120243506903829501.zip::Unternehmerabrechnung - VP 120-2400000990.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis November 2024.pdf</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>82.85</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift382024zaharievmartin3.zip::Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Oktober 2024.pdf</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6607,7 +6607,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift382024zaharievmartin3.zip::Leistungsnachweis Oktober 2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis September 2024.pdf</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6649,7 +6649,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift422024zaharievmartin3.zip::Leistungsnachweis November 2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Subunternehmer Sachsenpower GmbH &amp; Co. KG.pdf</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6691,7 +6691,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift442024zaharievmartin3.zip::Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Zahariev April 25 Sachsenpower GmbH &amp; Co. KG.pdf</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift442024zaharievmartin3.zip::Leistungsnachweis Dezember Zahariev 2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Zahariev Juli 2024.pdf</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6775,7 +6775,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>76.54</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschriftapril2025zahariev_pdf.zip::gutschrift April 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Zahariev Juni 25 Sachsenpower GmbH &amp; Co. KG.pdf</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6817,7 +6817,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschriftapril2025zahariev_pdf.zip::Leistungsnachweis Zahariev April 25 Sachsenpower GmbH &amp; Co. KG.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Zahariev Mai 25 Sachsenpower GmbH &amp; Co. KG.pdf</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6859,7 +6859,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>79.29</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschriftmrz2025zahariev_pdf.zip::gutschrift märz 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6901,7 +6901,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>103.00</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschriftmrz2025zahariev_pdf.zip::Leistungsnachweis Subunternehmer Sachsenpower GmbH &amp; Co. KG.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweismartinzaharievfe.zip::Leistungsnachweis Martin Zahariev Februar 2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6985,7 +6985,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>95.59</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweismartinzaharievfe.zip::Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7027,7 +7027,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2035-08</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweiszaharievjuli2024.zip::Leistungsnachweis Zahariev Juli 2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7069,12 +7069,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>75.47</t>
+          <t>11648.45</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweiszaharievjuli2024.zip::Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>181.48</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweiszaharievjuni25s.zip::Leistungsnachweis Zahariev Juni 25 Sachsenpower GmbH &amp; Co. KG.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7153,12 +7153,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2055-07</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>7847.85</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweiszaharievjuni25s.zip::Gutschrift Zahariev 74 30.06.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7195,7 +7195,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2056-07</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>79.29</t>
+          <t>163.63</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievgutschrift4831_01_.zip::Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7237,7 +7237,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2057-07</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievgutschrift4831_01_.zip::Leistungsnachweis Martin Zahariev Januar 2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7279,12 +7279,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2069-08</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>675.92</t>
+          <t>2763.67</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7321,12 +7321,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2070-08</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>11648.45</t>
+          <t>98.18</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7363,7 +7363,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>181.48</t>
+          <t>10390.09</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7405,7 +7405,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>196.35</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -7447,12 +7447,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2054-07</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>637.84</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -7489,12 +7489,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2055-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>7847.85</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -7531,7 +7531,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2056-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>163.63</t>
+          <t>1545.27</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -7573,7 +7573,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2057-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>94.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -7615,7 +7615,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2070-08</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>98.18</t>
+          <t>1309.21</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte207008_0.zip::Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2781 Zahariev Hermes Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7657,7 +7657,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2069-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2763.67</t>
+          <t>3042.12</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte207008_0.zip::Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2798 Zahariev Hermes Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -7699,12 +7699,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>599.76</t>
+          <t>1099.78</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2812 Zahariev Hermes Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -7741,12 +7741,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>499.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -7783,12 +7783,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1309.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7813,810 +7813,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2781 Zahariev Hermes Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53652_2024 20.09.2024 10_56_50.pdf</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>35.70</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>30.06</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Zahlungsavis Zahariev Juni 2025.pdf</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>166.60</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2814 zahariev bekleidung.pdf</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>47.60</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>1099.78</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2812 Zahariev Hermes Sendungsverlust.pdf</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>rent</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>333.20</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2811 Zahariev scannermiete.pdf</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>9496.20</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2810 Zahariev TF Touren.pdf</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>fuel</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrebestellung465795beiwebergmbh.zip::agb_doc.pdf</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>fuel</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrebestellung465795beiwebergmbh.zip::widerruf_doc.pdf</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungen.zip::working hours 06.2025  _____.xlsx</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>2018-05</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>fuel</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>-Identifikationsnummer: DE63ZZZ00000008438</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungen3333.zip::BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungenapril2025.zip::working hours 04.2025.xlsx</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungendezember2024.zip::working hours 12.2024.xlsx</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/testpayrollandworkinghours.zip::working hours 03.2025.xlsx</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/testpayslip.zip::38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/updatedworkinghoursinflationsprmie.zip::working hours 05.2024.xlsx</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/updatedworkinghoursinflationsprmie.zip::38389 - Vorgangsmappe Lohn - Auszahlungen Inflationsprämie.xlsx</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>435.00</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/wgprqualifikationkepkdnr_60222rechnungjahresgeb.zip::20240123_60222_10160_Rechnung.pdf</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>accounting fees</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/wgprqualifikationkepkdnr_60222rechnungjahresgeb.zip::3.0.2_920_v6.2_20240101_gebuehrenordnung_pq_kep.pdf</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>LOW</t>
         </is>
       </c>
     </row>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/operating_costs_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/operating_costs_timeline.xlsx
@@ -895,7 +895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/3.0.2_920_v6.2_20240101_gebuehrenordnung_pq_kep.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t/>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -967,24 +967,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/aktuelle Unbedenklichkeitsbescheinigungen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t/>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>8.02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/aktuelle Unbedenklichkeitsbescheinigungen.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t/>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>13649.05</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1261,19 +1261,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t/>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13447.05</t>
+          <t>13649.05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>41544.44</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>13447.05</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1357,91 +1357,91 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>vertreter</t>
+          <t/>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>88.53</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t/>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>vertreter</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t/>
+          <t>31.08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>5.20</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t/>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/UB.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2052.97</t>
+          <t/>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/UB.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2912.00</t>
+          <t>2052.97</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/2022 Arbeitgeberbestätigung zu den Arbeitstagen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3080.00</t>
+          <t>2912.00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/2023 Arbeitgeberbestätigung zu den Arbeitstagen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/2022 Arbeitgeberbestätigung zu den Arbeitstagen.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t/>
+          <t>3080.00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1597,24 +1597,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/2023 Arbeitgeberbestätigung zu den Arbeitstagen.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t/>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>30281.89</t>
+          <t/>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1634,24 +1634,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t/>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/39922 - Accountings 11-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>25150.59</t>
+          <t>30281.89</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/40578 - Accountings 12-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/39922 - Accountings 11-2023.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>18516.48</t>
+          <t>25150.59</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/40578 - Accountings 12-2023.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>30.10</t>
+          <t>18516.48</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20797.47</t>
+          <t>30.10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>24159.32</t>
+          <t>20797.47</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2024.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22523.36</t>
+          <t>24159.32</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2025.pdf</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1903,7 +1903,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22853.99</t>
+          <t>22523.36</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 04-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24018.01</t>
+          <t>22853.99</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 04-2024.pdf</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23553.36</t>
+          <t>24018.01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 06-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2029,7 +2029,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>23067.09</t>
+          <t>23553.36</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 07-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 06-2024.pdf</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22536.76</t>
+          <t>23067.09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 09-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 07-2024.pdf</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>24226.58</t>
+          <t>22536.76</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 10-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 09-2024.pdf</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2155,7 +2155,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>27948.98</t>
+          <t>24226.58</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 10-2024.pdf</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2197,7 +2197,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>23984.73</t>
+          <t>27948.98</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 12-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2239,12 +2239,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t/>
+          <t>23984.73</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2264,29 +2264,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t/>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 12-2024.pdf</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t/>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>797.30</t>
+          <t/>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2311,24 +2311,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>repairs</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>797.30</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Voransicht2023_89878877.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2365,12 +2365,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>repairs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2395,24 +2395,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/widerruf_doc.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Voransicht2023_89878877.pdf</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t/>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/working hours 03.2025.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/widerruf_doc.pdf</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2449,12 +2449,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t/>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2479,19 +2479,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/01-2023 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/working hours 03.2025.xlsx</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/01-2023 #9120.pdf</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2533,12 +2533,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t/>
+          <t>8.03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t/>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/03-2023 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2575,12 +2575,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t/>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t/>
+          <t>15.03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/03-2023 #9120.pdf</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2617,12 +2617,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2743,12 +2743,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2785,12 +2785,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>435.00</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t/>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2827,22 +2827,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-Identifikationsnummer: DE63ZZZ00000008438</t>
+          <t/>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t/>
+          <t>435.00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2857,34 +2857,34 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>-Id</t>
+          <t>-Identifikationsnummer: DE63ZZZ00000008438</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t/>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2899,19 +2899,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4025268_vom_01.09.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4026904_vom_01.11.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4025268_vom_01.09.2024.pdf</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2953,7 +2953,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>10.99</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4029768_vom_01.03.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4026904_vom_01.11.2024.pdf</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2995,7 +2995,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4030475_vom_01.04.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4029768_vom_01.03.2025.pdf</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4033045_vom_01.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4030475_vom_01.04.2025.pdf</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4034294_vom_01.09.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4033045_vom_01.08.2025.pdf</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t/>
+          <t>-Id</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _9005483_vom_04.07.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4034294_vom_01.09.2025.pdf</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3163,7 +3163,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>-ID: DE07ZZZ00000843064</t>
+          <t/>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t/>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3193,34 +3193,34 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Aktivierung Ihres SEPA-Mandats.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _9005483_vom_04.07.2025.pdf</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-Identifikationsnummer</t>
+          <t>-ID: DE07ZZZ00000843064</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t/>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3235,19 +3235,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Aktivierung Ihres SEPA-Mandats.PDF</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t/>
+          <t>-Identifikationsnummer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1928.00</t>
+          <t>31.08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3457,12 +3457,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t/>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>895.36</t>
+          <t>1928.00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>546.15</t>
+          <t>895.36</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>812.26</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3583,12 +3583,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2520.00</t>
+          <t>812.26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Schwerbehindertenabgabe _Überweisungsdaten.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1680.00</t>
+          <t>2520.00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/ueberweisung2022_89878877_20240612110113.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Schwerbehindertenabgabe _Überweisungsdaten.pdf</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3667,7 +3667,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Nr.: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>826119991.48</t>
+          <t>1680.00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Zahlungsavis 8345-1440-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/ueberweisung2022_89878877_20240612110113.pdf</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3709,7 +3709,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t/>
+          <t>Nr.: 2000016306</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>826119991.48</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Zahlungsavis Zahariev Juni 2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Zahlungsavis 8345-1440-1.pdf</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3751,7 +3751,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t/>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/3.0.2_920_v6.2_20240101_gebuehrenordnung_pq_kep.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Zahlungsavis Zahariev Juni 2025.pdf</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/operating_costs_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/operating_costs_timeline.xlsx
@@ -1438,12 +1438,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>675.92</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>betrag:_____ 675,92 €</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t/>
+          <t>Betrag</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1495,7 +1495,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>675.92</t>
+          <t>637.84</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>betrag:_____ 675,92 €</t>
+          <t>betrag:_____ 637,84 €</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1552,7 +1552,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t/>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>637.84</t>
+          <t>499.80</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>betrag:_____ 637,84 €</t>
+          <t>betrag: _____ 499,80 €</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>499.80</t>
+          <t>599.76</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>betrag: _____ 499,80 €</t>
+          <t>betrag:_____ 599,76 €</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1780,12 +1780,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>599.76</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>betrag:_____ 599,76 €</t>
+          <t>betrag: _____ 35,70 €</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1837,12 +1837,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t/>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>523.60</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>betrag: _____ 35,70 €</t>
+          <t>betrag:_____ 523,60 €</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>523.60</t>
+          <t>8282.40</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>betrag:_____ 523,60 €</t>
+          <t>betrag: _____ 8.282,40 €</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>vehicle costs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8282.40</t>
+          <t>71.40</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>betrag: _____ 8.282,40 €</t>
+          <t>betrag: _____ 71,40 €</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2008,12 +2008,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>vehicle costs</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>71.40</t>
+          <t>53.55</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>betrag: _____ 71,40 €</t>
+          <t>betrag: _____ 53,55 €</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t/>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>53.55</t>
+          <t>9496.20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>betrag: _____ 53,55 €</t>
+          <t>betrag: _____ 9.496,20 €</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9496.20</t>
+          <t>333.20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>betrag: _____ 9.496,20 €</t>
+          <t>betrag:_____ 333,20 €</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2179,12 +2179,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>accounting fees</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>333.20</t>
+          <t>47.60</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>betrag:_____ 333,20 €</t>
+          <t>betrag: _____ 47,60 €</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t/>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>47.60</t>
+          <t>166.60</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>betrag: _____ 47,60 €</t>
+          <t>betrag:_____ 166,60 €</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>accounting fees</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>166.60</t>
+          <t>2034.28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>betrag:_____ 166,60 €</t>
+          <t>Gesamtbetrag 2.034,28 EUR</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Betrag</t>
+          <t>Gesamtbetrag</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2034.28</t>
+          <t>176843.58</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Gesamtbetrag 2.034,28 EUR</t>
+          <t>Gesamtbetrag 176.843,58 EUR</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2407,7 +2407,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>176843.58</t>
+          <t>119991.48</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Gesamtbetrag 176.843,58 EUR</t>
+          <t>Gesamtbetrag 119.991,48 EUR</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>119991.48</t>
+          <t>34171.33</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Gesamtbetrag 119.991,48 EUR</t>
+          <t>Gesamtbetrag 34.171,33 EUR</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>34171.33</t>
+          <t>6242.25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Gesamtbetrag 34.171,33 EUR</t>
+          <t>Gesamtbetrag 6.242,25 EUR</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6242.25</t>
+          <t>634.21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Gesamtbetrag 6.242,25 EUR</t>
+          <t>Gesamtbetrag 634,21 EUR</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>634.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Gesamtbetrag 634,21 EUR</t>
+          <t>Gesamtbetrag 4,90 EUR</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2692,7 +2692,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>2543.30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gesamtbetrag 4,90 EUR</t>
+          <t>Gesamtbetrag 2.543,30 EUR</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>en-Nr: 2000016306</t>
+          <t/>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2543.30</t>
+          <t>608.64</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Gesamtbetrag 2.543,30 EUR</t>
+          <t>Gesamtbetrag 608,64 EUR</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2798,63 +2798,6 @@
         </is>
       </c>
       <c r="K49" t="inlineStr">
-        <is>
-          <t>operating_category_labeled_amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>fuel</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>en-Nr: 2000016306</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>608.64</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Gesamtbetrag 608,64 EUR</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Gesamtbetrag</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
         <is>
           <t>operating_category_labeled_amount</t>
         </is>
